--- a/Time to Fixation Experiments - Changing Chemotaxis Equation/Experiment 2 - Comparing Diffusion to Chemotaxis/Time_for_Bac_Fix_Comparison.xlsx
+++ b/Time to Fixation Experiments - Changing Chemotaxis Equation/Experiment 2 - Comparing Diffusion to Chemotaxis/Time_for_Bac_Fix_Comparison.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\Experiment 2 - Comparing Diffusion to Chemotaxis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\Time to Fixation Experiments - Changing Chemotaxis Equation\Experiment 2 - Comparing Diffusion to Chemotaxis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE646945-2788-47AB-BBBC-5A12D0124624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1744572-349C-4A66-B4EC-31D411682A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{C5D5DF43-D68A-448F-BEE9-BC751A2734F3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C5D5DF43-D68A-448F-BEE9-BC751A2734F3}"/>
   </bookViews>
   <sheets>
     <sheet name="All Time Distributions" sheetId="2" r:id="rId1"/>
@@ -110,12 +110,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -452,802 +451,802 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>19232</v>
+        <v>16634</v>
       </c>
       <c r="B2">
-        <v>25479</v>
+        <v>19759</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>11287</v>
+        <v>22472</v>
       </c>
       <c r="B3">
-        <v>23572</v>
+        <v>21205</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>21931</v>
+        <v>15586</v>
       </c>
       <c r="B4">
-        <v>22680</v>
+        <v>24775</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>19650</v>
+        <v>15735</v>
       </c>
       <c r="B5">
-        <v>27111</v>
+        <v>20404</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>26696</v>
+        <v>15363</v>
       </c>
       <c r="B6">
-        <v>27574</v>
+        <v>19818</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>17714</v>
+        <v>16444</v>
       </c>
       <c r="B7">
-        <v>22561</v>
+        <v>19107</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>25094</v>
+        <v>16198</v>
       </c>
       <c r="B8">
-        <v>29898</v>
+        <v>15866</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>28007</v>
+        <v>17846</v>
       </c>
       <c r="B9">
-        <v>22356</v>
+        <v>20245</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>18679</v>
+        <v>15841</v>
       </c>
       <c r="B10">
-        <v>29340</v>
+        <v>19851</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>19643</v>
+        <v>17363</v>
       </c>
       <c r="B11">
-        <v>23133</v>
+        <v>18618</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>19232</v>
+        <v>14760</v>
       </c>
       <c r="B12">
-        <v>30543</v>
+        <v>18521</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>11287</v>
+        <v>18310</v>
       </c>
       <c r="B13">
-        <v>29016</v>
+        <v>20627</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>21931</v>
+        <v>14800</v>
       </c>
       <c r="B14">
-        <v>22487</v>
+        <v>18372</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>19650</v>
+        <v>15814</v>
       </c>
       <c r="B15">
-        <v>22189</v>
+        <v>18594</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>26696</v>
+        <v>18416</v>
       </c>
       <c r="B16">
-        <v>21234</v>
+        <v>21549</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>17714</v>
+        <v>16894</v>
       </c>
       <c r="B17">
-        <v>24318</v>
+        <v>19314</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>25094</v>
+        <v>23383</v>
       </c>
       <c r="B18">
-        <v>22289</v>
+        <v>19146</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>28007</v>
+        <v>16284</v>
       </c>
       <c r="B19">
-        <v>25336</v>
+        <v>20854</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>18679</v>
+        <v>20268</v>
       </c>
       <c r="B20">
-        <v>25372</v>
+        <v>22689</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>19643</v>
+        <v>18299</v>
       </c>
       <c r="B21">
-        <v>19683</v>
+        <v>21217</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>21265</v>
+        <v>15518</v>
       </c>
       <c r="B22">
-        <v>25776</v>
+        <v>18080</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>21377</v>
+        <v>18258</v>
       </c>
       <c r="B23">
-        <v>26909</v>
+        <v>19725</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>22322</v>
+        <v>14661</v>
       </c>
       <c r="B24">
-        <v>28253</v>
+        <v>19012</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>24275</v>
+        <v>18435</v>
       </c>
       <c r="B25">
-        <v>27650</v>
+        <v>27235</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>30816</v>
+        <v>15699</v>
       </c>
       <c r="B26">
-        <v>26881</v>
+        <v>19424</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>16545</v>
+        <v>17490</v>
       </c>
       <c r="B27">
-        <v>10800</v>
+        <v>21139</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>19903</v>
+        <v>17610</v>
       </c>
       <c r="B28">
-        <v>24028</v>
+        <v>9685</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>39176</v>
+        <v>19275</v>
       </c>
       <c r="B29">
-        <v>32241</v>
+        <v>19560</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>21530</v>
+        <v>15778</v>
       </c>
       <c r="B30">
-        <v>27336</v>
+        <v>20743</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>21976</v>
+        <v>16835</v>
       </c>
       <c r="B31">
-        <v>26020</v>
+        <v>20309</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>24713</v>
+        <v>17221</v>
       </c>
       <c r="B32">
-        <v>27785</v>
+        <v>19334</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>23243</v>
+        <v>15998</v>
       </c>
       <c r="B33">
-        <v>36116</v>
+        <v>19855</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>21561</v>
+        <v>15551</v>
       </c>
       <c r="B34">
-        <v>23131</v>
+        <v>21295</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>21740</v>
+        <v>16320</v>
       </c>
       <c r="B35">
-        <v>23689</v>
+        <v>19548</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>18463</v>
+        <v>17597</v>
       </c>
       <c r="B36">
-        <v>25583</v>
+        <v>20794</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>17179</v>
+        <v>16577</v>
       </c>
       <c r="B37">
-        <v>26749</v>
+        <v>17858</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>24412</v>
+        <v>17523</v>
       </c>
       <c r="B38">
-        <v>21655</v>
+        <v>20599</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>26431</v>
+        <v>16864</v>
       </c>
       <c r="B39">
-        <v>6792</v>
+        <v>20101</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>23323</v>
+        <v>17102</v>
       </c>
       <c r="B40">
-        <v>26589</v>
+        <v>19031</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>26872</v>
+        <v>17282</v>
       </c>
       <c r="B41">
-        <v>24613</v>
+        <v>20483</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>19027</v>
+        <v>16472</v>
       </c>
       <c r="B42">
-        <v>24126</v>
+        <v>20248</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>28879</v>
+        <v>14526</v>
       </c>
       <c r="B43">
-        <v>22769</v>
+        <v>18191</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>18884</v>
+        <v>16708</v>
       </c>
       <c r="B44">
-        <v>34003</v>
+        <v>21878</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>20187</v>
+        <v>17392</v>
       </c>
       <c r="B45">
-        <v>23840</v>
+        <v>25490</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>36209</v>
+        <v>18781</v>
       </c>
       <c r="B46">
-        <v>24015</v>
+        <v>6782</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>21322</v>
+        <v>17353</v>
       </c>
       <c r="B47">
-        <v>27152</v>
+        <v>20208</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>26316</v>
+        <v>19775</v>
       </c>
       <c r="B48">
-        <v>24951</v>
+        <v>18593</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>19711</v>
+        <v>16158</v>
       </c>
       <c r="B49">
-        <v>22722</v>
+        <v>20634</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>24521</v>
+        <v>15542</v>
       </c>
       <c r="B50">
-        <v>25137</v>
+        <v>18676</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>28146</v>
+        <v>19375</v>
       </c>
       <c r="B51">
-        <v>23155</v>
+        <v>24730</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>18798</v>
+        <v>16775</v>
       </c>
       <c r="B52">
-        <v>23006</v>
+        <v>18222</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>28569</v>
+        <v>14966</v>
       </c>
       <c r="B53">
-        <v>27796</v>
+        <v>17495</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>25077</v>
+        <v>18290</v>
       </c>
       <c r="B54">
-        <v>29204</v>
+        <v>24203</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>29094</v>
+        <v>16439</v>
       </c>
       <c r="B55">
-        <v>28927</v>
+        <v>22361</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>24085</v>
+        <v>16085</v>
       </c>
       <c r="B56">
-        <v>22924</v>
+        <v>18318</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>19852</v>
+        <v>15109</v>
       </c>
       <c r="B57">
-        <v>33235</v>
+        <v>18741</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>21048</v>
+        <v>16827</v>
       </c>
       <c r="B58">
-        <v>22867</v>
+        <v>22015</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>17948</v>
+        <v>17459</v>
       </c>
       <c r="B59">
-        <v>20071</v>
+        <v>20920</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>16730</v>
+        <v>16333</v>
       </c>
       <c r="B60">
-        <v>21999</v>
+        <v>19273</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>22241</v>
+        <v>16709</v>
       </c>
       <c r="B61">
-        <v>34240</v>
+        <v>19909</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>12174</v>
+        <v>17258</v>
       </c>
       <c r="B62">
-        <v>29276</v>
+        <v>21759</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>28310</v>
+        <v>14761</v>
       </c>
       <c r="B63">
-        <v>31260</v>
+        <v>17351</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>19955</v>
+        <v>16775</v>
       </c>
       <c r="B64">
-        <v>27076</v>
+        <v>22677</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>22235</v>
+        <v>14020</v>
       </c>
       <c r="B65">
-        <v>18543</v>
+        <v>22067</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>18482</v>
+        <v>16239</v>
       </c>
       <c r="B66">
-        <v>28416</v>
+        <v>18337</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>16728</v>
+        <v>14369</v>
       </c>
       <c r="B67">
-        <v>25600</v>
+        <v>18601</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>13341</v>
+        <v>17432</v>
       </c>
       <c r="B68">
-        <v>32846</v>
+        <v>18654</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>20871</v>
+        <v>17718</v>
       </c>
       <c r="B69">
-        <v>22337</v>
+        <v>20312</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>29148</v>
+        <v>15054</v>
       </c>
       <c r="B70">
-        <v>23836</v>
+        <v>19596</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>19996</v>
+        <v>14690</v>
       </c>
       <c r="B71">
-        <v>24079</v>
+        <v>17557</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>21397</v>
+        <v>18087</v>
       </c>
       <c r="B72">
-        <v>20540</v>
+        <v>19684</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>19346</v>
+        <v>15455</v>
       </c>
       <c r="B73">
-        <v>26668</v>
+        <v>18818</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>24691</v>
+        <v>17360</v>
       </c>
       <c r="B74">
-        <v>22659</v>
+        <v>18888</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>20727</v>
+        <v>20873</v>
       </c>
       <c r="B75">
-        <v>31241</v>
+        <v>20777</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>19232</v>
+        <v>17800</v>
       </c>
       <c r="B76">
-        <v>21113</v>
+        <v>19199</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>11287</v>
+        <v>17082</v>
       </c>
       <c r="B77">
-        <v>25566</v>
+        <v>20639</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>21931</v>
+        <v>17010</v>
       </c>
       <c r="B78">
-        <v>23726</v>
+        <v>19413</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>19650</v>
+        <v>16223</v>
       </c>
       <c r="B79">
-        <v>36392</v>
+        <v>24694</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>26696</v>
+        <v>20619</v>
       </c>
       <c r="B80">
-        <v>16003</v>
+        <v>18393</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>17714</v>
+        <v>17068</v>
       </c>
       <c r="B81">
-        <v>34629</v>
+        <v>20395</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>19232</v>
+        <v>18559</v>
       </c>
       <c r="B82">
-        <v>25312</v>
+        <v>22067</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>11287</v>
+        <v>16719</v>
       </c>
       <c r="B83">
-        <v>28024</v>
+        <v>20997</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>21931</v>
+        <v>18323</v>
       </c>
       <c r="B84">
-        <v>29907</v>
+        <v>23621</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>19650</v>
+        <v>16893</v>
       </c>
       <c r="B85">
-        <v>26474</v>
+        <v>19785</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>17714</v>
+        <v>19397</v>
       </c>
       <c r="B86">
-        <v>28268</v>
+        <v>19621</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>25094</v>
+        <v>17573</v>
       </c>
       <c r="B87">
-        <v>25454</v>
+        <v>21327</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>28007</v>
+        <v>16644</v>
       </c>
       <c r="B88">
-        <v>24429</v>
+        <v>21650</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>18679</v>
+        <v>16510</v>
       </c>
       <c r="B89">
-        <v>6744</v>
+        <v>22856</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>19643</v>
+        <v>17834</v>
       </c>
       <c r="B90">
-        <v>29995</v>
+        <v>18524</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>21265</v>
+        <v>16340</v>
       </c>
       <c r="B91">
-        <v>28028</v>
+        <v>20209</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>21377</v>
+        <v>17189</v>
       </c>
       <c r="B92">
-        <v>7447</v>
+        <v>22606</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>22322</v>
+        <v>15984</v>
       </c>
       <c r="B93">
-        <v>30418</v>
+        <v>21839</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>16545</v>
+        <v>17181</v>
       </c>
       <c r="B94">
-        <v>31855</v>
+        <v>23308</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>19903</v>
+        <v>17910</v>
       </c>
       <c r="B95">
-        <v>22513</v>
+        <v>17418</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>21530</v>
+        <v>18310</v>
       </c>
       <c r="B96">
-        <v>36457</v>
+        <v>20593</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>21976</v>
+        <v>15632</v>
       </c>
       <c r="B97">
-        <v>30821</v>
+        <v>19385</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>23243</v>
+        <v>17093</v>
       </c>
       <c r="B98">
-        <v>31131</v>
+        <v>20579</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>21561</v>
+        <v>23264</v>
       </c>
       <c r="B99">
-        <v>27318</v>
+        <v>18450</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>21740</v>
+        <v>15585</v>
       </c>
       <c r="B100">
-        <v>28223</v>
+        <v>19071</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>18463</v>
+        <v>12418</v>
       </c>
       <c r="B101">
-        <v>17486</v>
+        <v>19449</v>
       </c>
     </row>
   </sheetData>
@@ -1261,1008 +1260,1008 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>19232</v>
+      <c r="A2">
+        <v>16634</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>11287</v>
+      <c r="A3">
+        <v>22472</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>21931</v>
+      <c r="A4">
+        <v>15586</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>19650</v>
+      <c r="A5">
+        <v>15735</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>26696</v>
+      <c r="A6">
+        <v>15363</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>17714</v>
+      <c r="A7">
+        <v>16444</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>25094</v>
+      <c r="A8">
+        <v>16198</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>28007</v>
+      <c r="A9">
+        <v>17846</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>18679</v>
+      <c r="A10">
+        <v>15841</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>19643</v>
+      <c r="A11">
+        <v>17363</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>19232</v>
+      <c r="A12">
+        <v>14760</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>11287</v>
+      <c r="A13">
+        <v>18310</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>21931</v>
+      <c r="A14">
+        <v>14800</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
-        <v>19650</v>
+      <c r="A15">
+        <v>15814</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
-        <v>26696</v>
+      <c r="A16">
+        <v>18416</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
-        <v>17714</v>
+      <c r="A17">
+        <v>16894</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
-        <v>25094</v>
+      <c r="A18">
+        <v>23383</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
-        <v>28007</v>
+      <c r="A19">
+        <v>16284</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
-        <v>18679</v>
+      <c r="A20">
+        <v>20268</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>19643</v>
+      <c r="A21">
+        <v>18299</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
-        <v>21265</v>
+      <c r="A22">
+        <v>15518</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
-        <v>21377</v>
+      <c r="A23">
+        <v>18258</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
-        <v>22322</v>
+      <c r="A24">
+        <v>14661</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
-        <v>24275</v>
+      <c r="A25">
+        <v>18435</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
-        <v>30816</v>
+      <c r="A26">
+        <v>15699</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
-        <v>16545</v>
+      <c r="A27">
+        <v>17490</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
-        <v>19903</v>
+      <c r="A28">
+        <v>17610</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
-        <v>39176</v>
+      <c r="A29">
+        <v>19275</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
-        <v>21530</v>
+      <c r="A30">
+        <v>15778</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
-        <v>21976</v>
+      <c r="A31">
+        <v>16835</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
-        <v>24713</v>
+      <c r="A32">
+        <v>17221</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
-        <v>23243</v>
+      <c r="A33">
+        <v>15998</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
-        <v>21561</v>
+      <c r="A34">
+        <v>15551</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
-        <v>21740</v>
+      <c r="A35">
+        <v>16320</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
-        <v>18463</v>
+      <c r="A36">
+        <v>17597</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
-        <v>17179</v>
+      <c r="A37">
+        <v>16577</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
-        <v>24412</v>
+      <c r="A38">
+        <v>17523</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
-        <v>26431</v>
+      <c r="A39">
+        <v>16864</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
-        <v>23323</v>
+      <c r="A40">
+        <v>17102</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
-        <v>26872</v>
+      <c r="A41">
+        <v>17282</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
-        <v>19027</v>
+      <c r="A42">
+        <v>16472</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
-        <v>28879</v>
+      <c r="A43">
+        <v>14526</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
-        <v>18884</v>
+      <c r="A44">
+        <v>16708</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
-        <v>20187</v>
+      <c r="A45">
+        <v>17392</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
-        <v>36209</v>
+      <c r="A46">
+        <v>18781</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
-        <v>21322</v>
+      <c r="A47">
+        <v>17353</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
-        <v>26316</v>
+      <c r="A48">
+        <v>19775</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
-        <v>19711</v>
+      <c r="A49">
+        <v>16158</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
-        <v>24521</v>
+      <c r="A50">
+        <v>15542</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
-        <v>28146</v>
+      <c r="A51">
+        <v>19375</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
-        <v>18798</v>
+      <c r="A52">
+        <v>16775</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
-        <v>28569</v>
+      <c r="A53">
+        <v>14966</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
-        <v>25077</v>
+      <c r="A54">
+        <v>18290</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
-        <v>29094</v>
+      <c r="A55">
+        <v>16439</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
-        <v>24085</v>
+      <c r="A56">
+        <v>16085</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
-        <v>19852</v>
+      <c r="A57">
+        <v>15109</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
-        <v>21048</v>
+      <c r="A58">
+        <v>16827</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="2">
-        <v>17948</v>
+      <c r="A59">
+        <v>17459</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
-        <v>16730</v>
+      <c r="A60">
+        <v>16333</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
-        <v>22241</v>
+      <c r="A61">
+        <v>16709</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
-        <v>12174</v>
+      <c r="A62">
+        <v>17258</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
-        <v>28310</v>
+      <c r="A63">
+        <v>14761</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="2">
-        <v>19955</v>
+      <c r="A64">
+        <v>16775</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
-        <v>22235</v>
+      <c r="A65">
+        <v>14020</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
-        <v>18482</v>
+      <c r="A66">
+        <v>16239</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
-        <v>16728</v>
+      <c r="A67">
+        <v>14369</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
-        <v>13341</v>
+      <c r="A68">
+        <v>17432</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
-        <v>20871</v>
+      <c r="A69">
+        <v>17718</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="2">
-        <v>29148</v>
+      <c r="A70">
+        <v>15054</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
-        <v>19996</v>
+      <c r="A71">
+        <v>14690</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
-        <v>21397</v>
+      <c r="A72">
+        <v>18087</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
-        <v>19346</v>
+      <c r="A73">
+        <v>15455</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
-        <v>24691</v>
+      <c r="A74">
+        <v>17360</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="2">
-        <v>20727</v>
+      <c r="A75">
+        <v>20873</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="2">
-        <v>19232</v>
+      <c r="A76">
+        <v>17800</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="2">
-        <v>11287</v>
+      <c r="A77">
+        <v>17082</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="2">
-        <v>21931</v>
+      <c r="A78">
+        <v>17010</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="2">
-        <v>19650</v>
+      <c r="A79">
+        <v>16223</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="2">
-        <v>26696</v>
+      <c r="A80">
+        <v>20619</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="2">
-        <v>17714</v>
+      <c r="A81">
+        <v>17068</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="2">
-        <v>19232</v>
+      <c r="A82">
+        <v>18559</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="2">
-        <v>11287</v>
+      <c r="A83">
+        <v>16719</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="2">
-        <v>21931</v>
+      <c r="A84">
+        <v>18323</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="2">
-        <v>19650</v>
+      <c r="A85">
+        <v>16893</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="2">
-        <v>17714</v>
+      <c r="A86">
+        <v>19397</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="2">
-        <v>25094</v>
+      <c r="A87">
+        <v>17573</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="2">
-        <v>28007</v>
+      <c r="A88">
+        <v>16644</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" s="2">
-        <v>18679</v>
+      <c r="A89">
+        <v>16510</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" s="2">
-        <v>19643</v>
+      <c r="A90">
+        <v>17834</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" s="2">
-        <v>21265</v>
+      <c r="A91">
+        <v>16340</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" s="2">
-        <v>21377</v>
+      <c r="A92">
+        <v>17189</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" s="2">
-        <v>22322</v>
+      <c r="A93">
+        <v>15984</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" s="2">
-        <v>16545</v>
+      <c r="A94">
+        <v>17181</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" s="2">
-        <v>19903</v>
+      <c r="A95">
+        <v>17910</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" s="2">
-        <v>21530</v>
+      <c r="A96">
+        <v>18310</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" s="2">
-        <v>21976</v>
+      <c r="A97">
+        <v>15632</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" s="2">
-        <v>23243</v>
+      <c r="A98">
+        <v>17093</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" s="2">
-        <v>21561</v>
+      <c r="A99">
+        <v>23264</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" s="2">
-        <v>21740</v>
+      <c r="A100">
+        <v>15585</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" s="2">
-        <v>18463</v>
+      <c r="A101">
+        <v>12418</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" s="2">
-        <v>25479</v>
+      <c r="A102">
+        <v>19759</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" s="2">
-        <v>23572</v>
+      <c r="A103">
+        <v>21205</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" s="2">
-        <v>22680</v>
+      <c r="A104">
+        <v>24775</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" s="2">
-        <v>27111</v>
+      <c r="A105">
+        <v>20404</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" s="2">
-        <v>27574</v>
+      <c r="A106">
+        <v>19818</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" s="2">
-        <v>22561</v>
+      <c r="A107">
+        <v>19107</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" s="2">
-        <v>29898</v>
+      <c r="A108">
+        <v>15866</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" s="2">
-        <v>22356</v>
+      <c r="A109">
+        <v>20245</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" s="2">
-        <v>29340</v>
+      <c r="A110">
+        <v>19851</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" s="2">
-        <v>23133</v>
+      <c r="A111">
+        <v>18618</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" s="2">
-        <v>30543</v>
+      <c r="A112">
+        <v>18521</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" s="2">
-        <v>29016</v>
+      <c r="A113">
+        <v>20627</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" s="2">
-        <v>22487</v>
+      <c r="A114">
+        <v>18372</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" s="2">
-        <v>22189</v>
+      <c r="A115">
+        <v>18594</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" s="2">
-        <v>21234</v>
+      <c r="A116">
+        <v>21549</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" s="2">
-        <v>24318</v>
+      <c r="A117">
+        <v>19314</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" s="2">
-        <v>22289</v>
+      <c r="A118">
+        <v>19146</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" s="2">
-        <v>25336</v>
+      <c r="A119">
+        <v>20854</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" s="2">
-        <v>25372</v>
+      <c r="A120">
+        <v>22689</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" s="2">
-        <v>19683</v>
+      <c r="A121">
+        <v>21217</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" s="2">
-        <v>25776</v>
+      <c r="A122">
+        <v>18080</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" s="2">
-        <v>26909</v>
+      <c r="A123">
+        <v>19725</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" s="2">
-        <v>28253</v>
+      <c r="A124">
+        <v>19012</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" s="2">
-        <v>27650</v>
+      <c r="A125">
+        <v>27235</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" s="2">
-        <v>26881</v>
+      <c r="A126">
+        <v>19424</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" s="2">
-        <v>10800</v>
+      <c r="A127">
+        <v>21139</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" s="2">
-        <v>24028</v>
+      <c r="A128">
+        <v>9685</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" s="2">
-        <v>32241</v>
+      <c r="A129">
+        <v>19560</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A130" s="2">
-        <v>27336</v>
+      <c r="A130">
+        <v>20743</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131" s="2">
-        <v>26020</v>
+      <c r="A131">
+        <v>20309</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" s="2">
-        <v>27785</v>
+      <c r="A132">
+        <v>19334</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" s="2">
-        <v>36116</v>
+      <c r="A133">
+        <v>19855</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A134" s="2">
-        <v>23131</v>
+      <c r="A134">
+        <v>21295</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A135" s="2">
-        <v>23689</v>
+      <c r="A135">
+        <v>19548</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A136" s="2">
-        <v>25583</v>
+      <c r="A136">
+        <v>20794</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A137" s="2">
-        <v>26749</v>
+      <c r="A137">
+        <v>17858</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A138" s="2">
-        <v>21655</v>
+      <c r="A138">
+        <v>20599</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" s="2">
-        <v>6792</v>
+      <c r="A139">
+        <v>20101</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" s="2">
-        <v>26589</v>
+      <c r="A140">
+        <v>19031</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A141" s="2">
-        <v>24613</v>
+      <c r="A141">
+        <v>20483</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142" s="2">
-        <v>24126</v>
+      <c r="A142">
+        <v>20248</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143" s="2">
-        <v>22769</v>
+      <c r="A143">
+        <v>18191</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" s="2">
-        <v>34003</v>
+      <c r="A144">
+        <v>21878</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A145" s="2">
-        <v>23840</v>
+      <c r="A145">
+        <v>25490</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A146" s="2">
-        <v>24015</v>
+      <c r="A146">
+        <v>6782</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A147" s="2">
-        <v>27152</v>
+      <c r="A147">
+        <v>20208</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A148" s="2">
-        <v>24951</v>
+      <c r="A148">
+        <v>18593</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A149" s="2">
-        <v>22722</v>
+      <c r="A149">
+        <v>20634</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A150" s="2">
-        <v>25137</v>
+      <c r="A150">
+        <v>18676</v>
       </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A151" s="2">
-        <v>23155</v>
+      <c r="A151">
+        <v>24730</v>
       </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A152" s="2">
-        <v>23006</v>
+      <c r="A152">
+        <v>18222</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A153" s="2">
-        <v>27796</v>
+      <c r="A153">
+        <v>17495</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A154" s="2">
-        <v>29204</v>
+      <c r="A154">
+        <v>24203</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A155" s="2">
-        <v>28927</v>
+      <c r="A155">
+        <v>22361</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A156" s="2">
-        <v>22924</v>
+      <c r="A156">
+        <v>18318</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A157" s="2">
-        <v>33235</v>
+      <c r="A157">
+        <v>18741</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A158" s="2">
-        <v>22867</v>
+      <c r="A158">
+        <v>22015</v>
       </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A159" s="2">
-        <v>20071</v>
+      <c r="A159">
+        <v>20920</v>
       </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A160" s="2">
-        <v>21999</v>
+      <c r="A160">
+        <v>19273</v>
       </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A161" s="2">
-        <v>34240</v>
+      <c r="A161">
+        <v>19909</v>
       </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A162" s="2">
-        <v>29276</v>
+      <c r="A162">
+        <v>21759</v>
       </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A163" s="2">
-        <v>31260</v>
+      <c r="A163">
+        <v>17351</v>
       </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A164" s="2">
-        <v>27076</v>
+      <c r="A164">
+        <v>22677</v>
       </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A165" s="2">
-        <v>18543</v>
+      <c r="A165">
+        <v>22067</v>
       </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A166" s="2">
-        <v>28416</v>
+      <c r="A166">
+        <v>18337</v>
       </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A167" s="2">
-        <v>25600</v>
+      <c r="A167">
+        <v>18601</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A168" s="2">
-        <v>32846</v>
+      <c r="A168">
+        <v>18654</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A169" s="2">
-        <v>22337</v>
+      <c r="A169">
+        <v>20312</v>
       </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A170" s="2">
-        <v>23836</v>
+      <c r="A170">
+        <v>19596</v>
       </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A171" s="2">
-        <v>24079</v>
+      <c r="A171">
+        <v>17557</v>
       </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A172" s="2">
-        <v>20540</v>
+      <c r="A172">
+        <v>19684</v>
       </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A173" s="2">
-        <v>26668</v>
+      <c r="A173">
+        <v>18818</v>
       </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A174" s="2">
-        <v>22659</v>
+      <c r="A174">
+        <v>18888</v>
       </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A175" s="2">
-        <v>31241</v>
+      <c r="A175">
+        <v>20777</v>
       </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A176" s="2">
-        <v>21113</v>
+      <c r="A176">
+        <v>19199</v>
       </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A177" s="2">
-        <v>25566</v>
+      <c r="A177">
+        <v>20639</v>
       </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A178" s="2">
-        <v>23726</v>
+      <c r="A178">
+        <v>19413</v>
       </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A179" s="2">
-        <v>36392</v>
+      <c r="A179">
+        <v>24694</v>
       </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A180" s="2">
-        <v>16003</v>
+      <c r="A180">
+        <v>18393</v>
       </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A181" s="2">
-        <v>34629</v>
+      <c r="A181">
+        <v>20395</v>
       </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A182" s="2">
-        <v>25312</v>
+      <c r="A182">
+        <v>22067</v>
       </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A183" s="2">
-        <v>28024</v>
+      <c r="A183">
+        <v>20997</v>
       </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A184" s="2">
-        <v>29907</v>
+      <c r="A184">
+        <v>23621</v>
       </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A185" s="2">
-        <v>26474</v>
+      <c r="A185">
+        <v>19785</v>
       </c>
     </row>
     <row r="186" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A186" s="2">
-        <v>28268</v>
+      <c r="A186">
+        <v>19621</v>
       </c>
     </row>
     <row r="187" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A187" s="2">
-        <v>25454</v>
+      <c r="A187">
+        <v>21327</v>
       </c>
     </row>
     <row r="188" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A188" s="2">
-        <v>24429</v>
+      <c r="A188">
+        <v>21650</v>
       </c>
     </row>
     <row r="189" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A189" s="2">
-        <v>6744</v>
+      <c r="A189">
+        <v>22856</v>
       </c>
     </row>
     <row r="190" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A190" s="2">
-        <v>29995</v>
+      <c r="A190">
+        <v>18524</v>
       </c>
     </row>
     <row r="191" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A191" s="2">
-        <v>28028</v>
+      <c r="A191">
+        <v>20209</v>
       </c>
     </row>
     <row r="192" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A192" s="2">
-        <v>7447</v>
+      <c r="A192">
+        <v>22606</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A193" s="2">
-        <v>30418</v>
+      <c r="A193">
+        <v>21839</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A194" s="2">
-        <v>31855</v>
+      <c r="A194">
+        <v>23308</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A195" s="2">
-        <v>22513</v>
+      <c r="A195">
+        <v>17418</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A196" s="2">
-        <v>36457</v>
+      <c r="A196">
+        <v>20593</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A197" s="2">
-        <v>30821</v>
+      <c r="A197">
+        <v>19385</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A198" s="2">
-        <v>31131</v>
+      <c r="A198">
+        <v>20579</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A199" s="2">
-        <v>27318</v>
+      <c r="A199">
+        <v>18450</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A200" s="2">
-        <v>28223</v>
+      <c r="A200">
+        <v>19071</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A201" s="2">
-        <v>17486</v>
+      <c r="A201">
+        <v>19449</v>
       </c>
     </row>
   </sheetData>
@@ -2292,1242 +2291,1102 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>19232</v>
+        <v>16634</v>
       </c>
       <c r="B2">
-        <v>320.53333333333336</v>
+        <v>277.23333333333335</v>
       </c>
       <c r="C2">
-        <v>5.3422222222222224</v>
+        <v>4.6205555555555557</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>11287</v>
+        <v>22472</v>
       </c>
       <c r="B3">
-        <v>188.11666666666667</v>
+        <v>374.53333333333336</v>
       </c>
       <c r="C3">
-        <v>3.1352777777777776</v>
+        <v>6.2422222222222219</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>21931</v>
+        <v>15586</v>
       </c>
       <c r="B4">
-        <v>365.51666666666665</v>
+        <v>259.76666666666665</v>
       </c>
       <c r="C4">
-        <v>6.0919444444444446</v>
+        <v>4.3294444444444444</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>19650</v>
+        <v>15735</v>
       </c>
       <c r="B5">
-        <v>327.5</v>
+        <v>262.25</v>
       </c>
       <c r="C5">
-        <v>5.458333333333333</v>
+        <v>4.3708333333333336</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>26696</v>
+        <v>15363</v>
       </c>
       <c r="B6">
-        <v>444.93333333333334</v>
+        <v>256.05</v>
       </c>
       <c r="C6">
-        <v>7.4155555555555557</v>
+        <v>4.2675000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>17714</v>
+        <v>16444</v>
       </c>
       <c r="B7">
-        <v>295.23333333333335</v>
+        <v>274.06666666666666</v>
       </c>
       <c r="C7">
-        <v>4.9205555555555556</v>
+        <v>4.5677777777777777</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>25094</v>
+        <v>16198</v>
       </c>
       <c r="B8">
-        <v>418.23333333333335</v>
+        <v>269.96666666666664</v>
       </c>
       <c r="C8">
-        <v>6.9705555555555554</v>
+        <v>4.4994444444444444</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>28007</v>
+        <v>17846</v>
       </c>
       <c r="B9">
-        <v>466.78333333333336</v>
+        <v>297.43333333333334</v>
       </c>
       <c r="C9">
-        <v>7.7797222222222224</v>
+        <v>4.9572222222222226</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>18679</v>
+        <v>15841</v>
       </c>
       <c r="B10">
-        <v>311.31666666666666</v>
+        <v>264.01666666666665</v>
       </c>
       <c r="C10">
-        <v>5.1886111111111113</v>
+        <v>4.4002777777777782</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>19643</v>
+        <v>17363</v>
       </c>
       <c r="B11">
-        <v>327.38333333333333</v>
+        <v>289.38333333333333</v>
       </c>
       <c r="C11">
-        <v>5.4563888888888892</v>
+        <v>4.8230555555555554</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>19232</v>
+        <v>14760</v>
       </c>
       <c r="B12">
-        <f>A12/60</f>
-        <v>320.53333333333336</v>
+        <v>246</v>
       </c>
       <c r="C12">
-        <f>A12/3600</f>
-        <v>5.3422222222222224</v>
+        <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>11287</v>
+        <v>18310</v>
       </c>
       <c r="B13">
-        <f t="shared" ref="B13:B76" si="0">A13/60</f>
-        <v>188.11666666666667</v>
+        <v>305.16666666666669</v>
       </c>
       <c r="C13">
-        <f t="shared" ref="C13:C76" si="1">A13/3600</f>
-        <v>3.1352777777777776</v>
+        <v>5.0861111111111112</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>21931</v>
+        <v>14800</v>
       </c>
       <c r="B14">
-        <f t="shared" si="0"/>
-        <v>365.51666666666665</v>
+        <v>246.66666666666666</v>
       </c>
       <c r="C14">
-        <f t="shared" si="1"/>
-        <v>6.0919444444444446</v>
+        <v>4.1111111111111107</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>19650</v>
+        <v>15814</v>
       </c>
       <c r="B15">
-        <f t="shared" si="0"/>
-        <v>327.5</v>
+        <v>263.56666666666666</v>
       </c>
       <c r="C15">
-        <f t="shared" si="1"/>
-        <v>5.458333333333333</v>
+        <v>4.3927777777777779</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>26696</v>
+        <v>18416</v>
       </c>
       <c r="B16">
-        <f t="shared" si="0"/>
-        <v>444.93333333333334</v>
+        <v>306.93333333333334</v>
       </c>
       <c r="C16">
-        <f t="shared" si="1"/>
-        <v>7.4155555555555557</v>
+        <v>5.1155555555555559</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>17714</v>
+        <v>16894</v>
       </c>
       <c r="B17">
-        <f t="shared" si="0"/>
-        <v>295.23333333333335</v>
+        <v>281.56666666666666</v>
       </c>
       <c r="C17">
-        <f t="shared" si="1"/>
-        <v>4.9205555555555556</v>
+        <v>4.6927777777777777</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>25094</v>
+        <v>23383</v>
       </c>
       <c r="B18">
-        <f t="shared" si="0"/>
-        <v>418.23333333333335</v>
+        <v>389.71666666666664</v>
       </c>
       <c r="C18">
-        <f t="shared" si="1"/>
-        <v>6.9705555555555554</v>
+        <v>6.4952777777777779</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>28007</v>
+        <v>16284</v>
       </c>
       <c r="B19">
-        <f t="shared" si="0"/>
-        <v>466.78333333333336</v>
+        <v>271.39999999999998</v>
       </c>
       <c r="C19">
-        <f t="shared" si="1"/>
-        <v>7.7797222222222224</v>
+        <v>4.5233333333333334</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>18679</v>
+        <v>20268</v>
       </c>
       <c r="B20">
-        <f t="shared" si="0"/>
-        <v>311.31666666666666</v>
+        <v>337.8</v>
       </c>
       <c r="C20">
-        <f t="shared" si="1"/>
-        <v>5.1886111111111113</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>19643</v>
+        <v>18299</v>
       </c>
       <c r="B21">
-        <f t="shared" si="0"/>
-        <v>327.38333333333333</v>
+        <v>304.98333333333335</v>
       </c>
       <c r="C21">
-        <f t="shared" si="1"/>
-        <v>5.4563888888888892</v>
+        <v>5.0830555555555552</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>21265</v>
+        <v>15518</v>
       </c>
       <c r="B22">
-        <f t="shared" si="0"/>
-        <v>354.41666666666669</v>
+        <v>258.63333333333333</v>
       </c>
       <c r="C22">
-        <f t="shared" si="1"/>
-        <v>5.9069444444444441</v>
+        <v>4.3105555555555553</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>21377</v>
+        <v>18258</v>
       </c>
       <c r="B23">
-        <f t="shared" si="0"/>
-        <v>356.28333333333336</v>
+        <v>304.3</v>
       </c>
       <c r="C23">
-        <f t="shared" si="1"/>
-        <v>5.9380555555555556</v>
+        <v>5.0716666666666663</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>22322</v>
+        <v>14661</v>
       </c>
       <c r="B24">
-        <f t="shared" si="0"/>
-        <v>372.03333333333336</v>
+        <v>244.35</v>
       </c>
       <c r="C24">
-        <f t="shared" si="1"/>
-        <v>6.2005555555555558</v>
+        <v>4.0724999999999998</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>24275</v>
+        <v>18435</v>
       </c>
       <c r="B25">
-        <f t="shared" si="0"/>
-        <v>404.58333333333331</v>
+        <v>307.25</v>
       </c>
       <c r="C25">
-        <f t="shared" si="1"/>
-        <v>6.7430555555555554</v>
+        <v>5.1208333333333336</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>30816</v>
+        <v>15699</v>
       </c>
       <c r="B26">
-        <f t="shared" si="0"/>
-        <v>513.6</v>
+        <v>261.64999999999998</v>
       </c>
       <c r="C26">
-        <f t="shared" si="1"/>
-        <v>8.56</v>
+        <v>4.3608333333333329</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>16545</v>
+        <v>17490</v>
       </c>
       <c r="B27">
-        <f t="shared" si="0"/>
-        <v>275.75</v>
+        <v>291.5</v>
       </c>
       <c r="C27">
-        <f t="shared" si="1"/>
-        <v>4.5958333333333332</v>
+        <v>4.8583333333333334</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>19903</v>
+        <v>17610</v>
       </c>
       <c r="B28">
-        <f t="shared" si="0"/>
-        <v>331.71666666666664</v>
+        <v>293.5</v>
       </c>
       <c r="C28">
-        <f t="shared" si="1"/>
-        <v>5.5286111111111111</v>
+        <v>4.8916666666666666</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>39176</v>
+        <v>19275</v>
       </c>
       <c r="B29">
-        <f t="shared" si="0"/>
-        <v>652.93333333333328</v>
+        <v>321.25</v>
       </c>
       <c r="C29">
-        <f t="shared" si="1"/>
-        <v>10.882222222222222</v>
+        <v>5.354166666666667</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>21530</v>
+        <v>15778</v>
       </c>
       <c r="B30">
-        <f t="shared" si="0"/>
-        <v>358.83333333333331</v>
+        <v>262.96666666666664</v>
       </c>
       <c r="C30">
-        <f t="shared" si="1"/>
-        <v>5.9805555555555552</v>
+        <v>4.3827777777777781</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>21976</v>
+        <v>16835</v>
       </c>
       <c r="B31">
-        <f t="shared" si="0"/>
-        <v>366.26666666666665</v>
+        <v>280.58333333333331</v>
       </c>
       <c r="C31">
-        <f t="shared" si="1"/>
-        <v>6.1044444444444448</v>
+        <v>4.6763888888888889</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>24713</v>
+        <v>17221</v>
       </c>
       <c r="B32">
-        <f t="shared" si="0"/>
-        <v>411.88333333333333</v>
+        <v>287.01666666666665</v>
       </c>
       <c r="C32">
-        <f t="shared" si="1"/>
-        <v>6.8647222222222224</v>
+        <v>4.783611111111111</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>23243</v>
+        <v>15998</v>
       </c>
       <c r="B33">
-        <f t="shared" si="0"/>
-        <v>387.38333333333333</v>
+        <v>266.63333333333333</v>
       </c>
       <c r="C33">
-        <f t="shared" si="1"/>
-        <v>6.4563888888888892</v>
+        <v>4.443888888888889</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>21561</v>
+        <v>15551</v>
       </c>
       <c r="B34">
-        <f t="shared" si="0"/>
-        <v>359.35</v>
+        <v>259.18333333333334</v>
       </c>
       <c r="C34">
-        <f t="shared" si="1"/>
-        <v>5.9891666666666667</v>
+        <v>4.3197222222222225</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>21740</v>
+        <v>16320</v>
       </c>
       <c r="B35">
-        <f t="shared" si="0"/>
-        <v>362.33333333333331</v>
+        <v>272</v>
       </c>
       <c r="C35">
-        <f t="shared" si="1"/>
-        <v>6.0388888888888888</v>
+        <v>4.5333333333333332</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>18463</v>
+        <v>17597</v>
       </c>
       <c r="B36">
-        <f t="shared" si="0"/>
-        <v>307.71666666666664</v>
+        <v>293.28333333333336</v>
       </c>
       <c r="C36">
-        <f t="shared" si="1"/>
-        <v>5.1286111111111108</v>
+        <v>4.8880555555555558</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>17179</v>
+        <v>16577</v>
       </c>
       <c r="B37">
-        <f t="shared" si="0"/>
-        <v>286.31666666666666</v>
+        <v>276.28333333333336</v>
       </c>
       <c r="C37">
-        <f t="shared" si="1"/>
-        <v>4.7719444444444443</v>
+        <v>4.6047222222222226</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>24412</v>
+        <v>17523</v>
       </c>
       <c r="B38">
-        <f t="shared" si="0"/>
-        <v>406.86666666666667</v>
+        <v>292.05</v>
       </c>
       <c r="C38">
-        <f t="shared" si="1"/>
-        <v>6.7811111111111115</v>
+        <v>4.8674999999999997</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>26431</v>
+        <v>16864</v>
       </c>
       <c r="B39">
-        <f t="shared" si="0"/>
-        <v>440.51666666666665</v>
+        <v>281.06666666666666</v>
       </c>
       <c r="C39">
-        <f t="shared" si="1"/>
-        <v>7.3419444444444446</v>
+        <v>4.6844444444444449</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>23323</v>
+        <v>17102</v>
       </c>
       <c r="B40">
-        <f t="shared" si="0"/>
-        <v>388.71666666666664</v>
+        <v>285.03333333333336</v>
       </c>
       <c r="C40">
-        <f t="shared" si="1"/>
-        <v>6.4786111111111113</v>
+        <v>4.7505555555555556</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>26872</v>
+        <v>17282</v>
       </c>
       <c r="B41">
-        <f t="shared" si="0"/>
-        <v>447.86666666666667</v>
+        <v>288.03333333333336</v>
       </c>
       <c r="C41">
-        <f t="shared" si="1"/>
-        <v>7.4644444444444442</v>
+        <v>4.8005555555555555</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>19027</v>
+        <v>16472</v>
       </c>
       <c r="B42">
-        <f t="shared" si="0"/>
-        <v>317.11666666666667</v>
+        <v>274.53333333333336</v>
       </c>
       <c r="C42">
-        <f t="shared" si="1"/>
-        <v>5.285277777777778</v>
+        <v>4.5755555555555558</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>28879</v>
+        <v>14526</v>
       </c>
       <c r="B43">
-        <f t="shared" si="0"/>
-        <v>481.31666666666666</v>
+        <v>242.1</v>
       </c>
       <c r="C43">
-        <f t="shared" si="1"/>
-        <v>8.0219444444444452</v>
+        <v>4.0350000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>18884</v>
+        <v>16708</v>
       </c>
       <c r="B44">
-        <f t="shared" si="0"/>
-        <v>314.73333333333335</v>
+        <v>278.46666666666664</v>
       </c>
       <c r="C44">
-        <f t="shared" si="1"/>
-        <v>5.2455555555555557</v>
+        <v>4.641111111111111</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>20187</v>
+        <v>17392</v>
       </c>
       <c r="B45">
-        <f t="shared" si="0"/>
-        <v>336.45</v>
+        <v>289.86666666666667</v>
       </c>
       <c r="C45">
-        <f t="shared" si="1"/>
-        <v>5.6074999999999999</v>
+        <v>4.8311111111111114</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>36209</v>
+        <v>18781</v>
       </c>
       <c r="B46">
-        <f t="shared" si="0"/>
-        <v>603.48333333333335</v>
+        <v>313.01666666666665</v>
       </c>
       <c r="C46">
-        <f t="shared" si="1"/>
-        <v>10.058055555555555</v>
+        <v>5.2169444444444446</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>21322</v>
+        <v>17353</v>
       </c>
       <c r="B47">
-        <f t="shared" si="0"/>
-        <v>355.36666666666667</v>
+        <v>289.21666666666664</v>
       </c>
       <c r="C47">
-        <f t="shared" si="1"/>
-        <v>5.9227777777777781</v>
+        <v>4.8202777777777781</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>26316</v>
+        <v>19775</v>
       </c>
       <c r="B48">
-        <f t="shared" si="0"/>
-        <v>438.6</v>
+        <v>329.58333333333331</v>
       </c>
       <c r="C48">
-        <f t="shared" si="1"/>
-        <v>7.31</v>
+        <v>5.4930555555555554</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>19711</v>
+        <v>16158</v>
       </c>
       <c r="B49">
-        <f t="shared" si="0"/>
-        <v>328.51666666666665</v>
+        <v>269.3</v>
       </c>
       <c r="C49">
-        <f t="shared" si="1"/>
-        <v>5.4752777777777775</v>
+        <v>4.4883333333333333</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>24521</v>
+        <v>15542</v>
       </c>
       <c r="B50">
-        <f t="shared" si="0"/>
-        <v>408.68333333333334</v>
+        <v>259.03333333333336</v>
       </c>
       <c r="C50">
-        <f t="shared" si="1"/>
-        <v>6.8113888888888887</v>
+        <v>4.3172222222222221</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>28146</v>
+        <v>19375</v>
       </c>
       <c r="B51">
-        <f t="shared" si="0"/>
-        <v>469.1</v>
+        <v>322.91666666666669</v>
       </c>
       <c r="C51">
-        <f t="shared" si="1"/>
-        <v>7.8183333333333334</v>
+        <v>5.3819444444444446</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>18798</v>
+        <v>16775</v>
       </c>
       <c r="B52">
-        <f t="shared" si="0"/>
-        <v>313.3</v>
+        <v>279.58333333333331</v>
       </c>
       <c r="C52">
-        <f t="shared" si="1"/>
-        <v>5.2216666666666667</v>
+        <v>4.6597222222222223</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>28569</v>
+        <v>14966</v>
       </c>
       <c r="B53">
-        <f t="shared" si="0"/>
-        <v>476.15</v>
+        <v>249.43333333333334</v>
       </c>
       <c r="C53">
-        <f t="shared" si="1"/>
-        <v>7.9358333333333331</v>
+        <v>4.1572222222222219</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>25077</v>
+        <v>18290</v>
       </c>
       <c r="B54">
-        <f t="shared" si="0"/>
-        <v>417.95</v>
+        <v>304.83333333333331</v>
       </c>
       <c r="C54">
-        <f t="shared" si="1"/>
-        <v>6.9658333333333333</v>
+        <v>5.0805555555555557</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>29094</v>
+        <v>16439</v>
       </c>
       <c r="B55">
-        <f t="shared" si="0"/>
-        <v>484.9</v>
+        <v>273.98333333333335</v>
       </c>
       <c r="C55">
-        <f t="shared" si="1"/>
-        <v>8.081666666666667</v>
+        <v>4.5663888888888886</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>24085</v>
+        <v>16085</v>
       </c>
       <c r="B56">
-        <f t="shared" si="0"/>
-        <v>401.41666666666669</v>
+        <v>268.08333333333331</v>
       </c>
       <c r="C56">
-        <f t="shared" si="1"/>
-        <v>6.6902777777777782</v>
+        <v>4.4680555555555559</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>19852</v>
+        <v>15109</v>
       </c>
       <c r="B57">
-        <f t="shared" si="0"/>
-        <v>330.86666666666667</v>
+        <v>251.81666666666666</v>
       </c>
       <c r="C57">
-        <f t="shared" si="1"/>
-        <v>5.514444444444444</v>
+        <v>4.1969444444444441</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>21048</v>
+        <v>16827</v>
       </c>
       <c r="B58">
-        <f t="shared" si="0"/>
-        <v>350.8</v>
+        <v>280.45</v>
       </c>
       <c r="C58">
-        <f t="shared" si="1"/>
-        <v>5.8466666666666667</v>
+        <v>4.6741666666666664</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>17948</v>
+        <v>17459</v>
       </c>
       <c r="B59">
-        <f t="shared" si="0"/>
-        <v>299.13333333333333</v>
+        <v>290.98333333333335</v>
       </c>
       <c r="C59">
-        <f t="shared" si="1"/>
-        <v>4.985555555555556</v>
+        <v>4.8497222222222218</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>16730</v>
+        <v>16333</v>
       </c>
       <c r="B60">
-        <f t="shared" si="0"/>
-        <v>278.83333333333331</v>
+        <v>272.21666666666664</v>
       </c>
       <c r="C60">
-        <f t="shared" si="1"/>
-        <v>4.6472222222222221</v>
+        <v>4.536944444444444</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>22241</v>
+        <v>16709</v>
       </c>
       <c r="B61">
-        <f t="shared" si="0"/>
-        <v>370.68333333333334</v>
+        <v>278.48333333333335</v>
       </c>
       <c r="C61">
-        <f t="shared" si="1"/>
-        <v>6.1780555555555559</v>
+        <v>4.6413888888888888</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>12174</v>
+        <v>17258</v>
       </c>
       <c r="B62">
-        <f t="shared" si="0"/>
-        <v>202.9</v>
+        <v>287.63333333333333</v>
       </c>
       <c r="C62">
-        <f t="shared" si="1"/>
-        <v>3.3816666666666668</v>
+        <v>4.7938888888888886</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>28310</v>
+        <v>14761</v>
       </c>
       <c r="B63">
-        <f t="shared" si="0"/>
-        <v>471.83333333333331</v>
+        <v>246.01666666666668</v>
       </c>
       <c r="C63">
-        <f t="shared" si="1"/>
-        <v>7.8638888888888889</v>
+        <v>4.1002777777777775</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>19955</v>
+        <v>16775</v>
       </c>
       <c r="B64">
-        <f t="shared" si="0"/>
-        <v>332.58333333333331</v>
+        <v>279.58333333333331</v>
       </c>
       <c r="C64">
-        <f t="shared" si="1"/>
-        <v>5.5430555555555552</v>
+        <v>4.6597222222222223</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>22235</v>
+        <v>14020</v>
       </c>
       <c r="B65">
-        <f t="shared" si="0"/>
-        <v>370.58333333333331</v>
+        <v>233.66666666666666</v>
       </c>
       <c r="C65">
-        <f t="shared" si="1"/>
-        <v>6.1763888888888889</v>
+        <v>3.8944444444444444</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>18482</v>
+        <v>16239</v>
       </c>
       <c r="B66">
-        <f t="shared" si="0"/>
-        <v>308.03333333333336</v>
+        <v>270.64999999999998</v>
       </c>
       <c r="C66">
-        <f t="shared" si="1"/>
-        <v>5.1338888888888885</v>
+        <v>4.5108333333333333</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>16728</v>
+        <v>14369</v>
       </c>
       <c r="B67">
-        <f t="shared" si="0"/>
-        <v>278.8</v>
+        <v>239.48333333333332</v>
       </c>
       <c r="C67">
-        <f t="shared" si="1"/>
-        <v>4.6466666666666665</v>
+        <v>3.9913888888888889</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>13341</v>
+        <v>17432</v>
       </c>
       <c r="B68">
-        <f t="shared" si="0"/>
-        <v>222.35</v>
+        <v>290.53333333333336</v>
       </c>
       <c r="C68">
-        <f t="shared" si="1"/>
-        <v>3.7058333333333335</v>
+        <v>4.8422222222222224</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>20871</v>
+        <v>17718</v>
       </c>
       <c r="B69">
-        <f t="shared" si="0"/>
-        <v>347.85</v>
+        <v>295.3</v>
       </c>
       <c r="C69">
-        <f t="shared" si="1"/>
-        <v>5.7975000000000003</v>
+        <v>4.9216666666666669</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>29148</v>
+        <v>15054</v>
       </c>
       <c r="B70">
-        <f t="shared" si="0"/>
-        <v>485.8</v>
+        <v>250.9</v>
       </c>
       <c r="C70">
-        <f t="shared" si="1"/>
-        <v>8.0966666666666658</v>
+        <v>4.1816666666666666</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>19996</v>
+        <v>14690</v>
       </c>
       <c r="B71">
-        <f t="shared" si="0"/>
-        <v>333.26666666666665</v>
+        <v>244.83333333333334</v>
       </c>
       <c r="C71">
-        <f t="shared" si="1"/>
-        <v>5.5544444444444441</v>
+        <v>4.0805555555555557</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>21397</v>
+        <v>18087</v>
       </c>
       <c r="B72">
-        <f t="shared" si="0"/>
-        <v>356.61666666666667</v>
+        <v>301.45</v>
       </c>
       <c r="C72">
-        <f t="shared" si="1"/>
-        <v>5.9436111111111112</v>
+        <v>5.0241666666666669</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>19346</v>
+        <v>15455</v>
       </c>
       <c r="B73">
-        <f t="shared" si="0"/>
-        <v>322.43333333333334</v>
+        <v>257.58333333333331</v>
       </c>
       <c r="C73">
-        <f t="shared" si="1"/>
-        <v>5.3738888888888887</v>
+        <v>4.2930555555555552</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>24691</v>
+        <v>17360</v>
       </c>
       <c r="B74">
-        <f t="shared" si="0"/>
-        <v>411.51666666666665</v>
+        <v>289.33333333333331</v>
       </c>
       <c r="C74">
-        <f t="shared" si="1"/>
-        <v>6.8586111111111112</v>
+        <v>4.822222222222222</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>20727</v>
+        <v>20873</v>
       </c>
       <c r="B75">
-        <f t="shared" si="0"/>
-        <v>345.45</v>
+        <v>347.88333333333333</v>
       </c>
       <c r="C75">
-        <f t="shared" si="1"/>
-        <v>5.7575000000000003</v>
+        <v>5.798055555555556</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>19232</v>
+        <v>17800</v>
       </c>
       <c r="B76">
-        <f t="shared" si="0"/>
-        <v>320.53333333333336</v>
+        <v>296.66666666666669</v>
       </c>
       <c r="C76">
-        <f t="shared" si="1"/>
-        <v>5.3422222222222224</v>
+        <v>4.9444444444444446</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>11287</v>
+        <v>17082</v>
       </c>
       <c r="B77">
-        <f t="shared" ref="B77:B81" si="2">A77/60</f>
-        <v>188.11666666666667</v>
+        <v>284.7</v>
       </c>
       <c r="C77">
-        <f t="shared" ref="C77:C81" si="3">A77/3600</f>
-        <v>3.1352777777777776</v>
+        <v>4.7450000000000001</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>21931</v>
+        <v>17010</v>
       </c>
       <c r="B78">
-        <f t="shared" si="2"/>
-        <v>365.51666666666665</v>
+        <v>283.5</v>
       </c>
       <c r="C78">
-        <f t="shared" si="3"/>
-        <v>6.0919444444444446</v>
+        <v>4.7249999999999996</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>19650</v>
+        <v>16223</v>
       </c>
       <c r="B79">
-        <f t="shared" si="2"/>
-        <v>327.5</v>
+        <v>270.38333333333333</v>
       </c>
       <c r="C79">
-        <f t="shared" si="3"/>
-        <v>5.458333333333333</v>
+        <v>4.506388888888889</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>26696</v>
+        <v>20619</v>
       </c>
       <c r="B80">
-        <f t="shared" si="2"/>
-        <v>444.93333333333334</v>
+        <v>343.65</v>
       </c>
       <c r="C80">
-        <f t="shared" si="3"/>
-        <v>7.4155555555555557</v>
+        <v>5.7275</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>17714</v>
+        <v>17068</v>
       </c>
       <c r="B81">
-        <f t="shared" si="2"/>
-        <v>295.23333333333335</v>
+        <v>284.46666666666664</v>
       </c>
       <c r="C81">
-        <f t="shared" si="3"/>
-        <v>4.9205555555555556</v>
+        <v>4.7411111111111115</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>19232</v>
+        <v>18559</v>
       </c>
       <c r="B82">
-        <v>320.53333333333336</v>
+        <v>309.31666666666666</v>
       </c>
       <c r="C82">
-        <v>5.3422222222222224</v>
+        <v>5.1552777777777781</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>11287</v>
+        <v>16719</v>
       </c>
       <c r="B83">
-        <v>188.11666666666667</v>
+        <v>278.64999999999998</v>
       </c>
       <c r="C83">
-        <v>3.1352777777777776</v>
+        <v>4.644166666666667</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>21931</v>
+        <v>18323</v>
       </c>
       <c r="B84">
-        <v>365.51666666666665</v>
+        <v>305.38333333333333</v>
       </c>
       <c r="C84">
-        <v>6.0919444444444446</v>
+        <v>5.089722222222222</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>19650</v>
+        <v>16893</v>
       </c>
       <c r="B85">
-        <v>327.5</v>
+        <v>281.55</v>
       </c>
       <c r="C85">
-        <v>5.458333333333333</v>
+        <v>4.6924999999999999</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>17714</v>
+        <v>19397</v>
       </c>
       <c r="B86">
-        <v>295.23333333333335</v>
+        <v>323.28333333333336</v>
       </c>
       <c r="C86">
-        <v>4.9205555555555556</v>
+        <v>5.3880555555555558</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>25094</v>
+        <v>17573</v>
       </c>
       <c r="B87">
-        <v>418.23333333333335</v>
+        <v>292.88333333333333</v>
       </c>
       <c r="C87">
-        <v>6.9705555555555554</v>
+        <v>4.881388888888889</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>28007</v>
+        <v>16644</v>
       </c>
       <c r="B88">
-        <v>466.78333333333336</v>
+        <v>277.39999999999998</v>
       </c>
       <c r="C88">
-        <v>7.7797222222222224</v>
+        <v>4.6233333333333331</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>18679</v>
+        <v>16510</v>
       </c>
       <c r="B89">
-        <v>311.31666666666666</v>
+        <v>275.16666666666669</v>
       </c>
       <c r="C89">
-        <v>5.1886111111111113</v>
+        <v>4.5861111111111112</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>19643</v>
+        <v>17834</v>
       </c>
       <c r="B90">
-        <v>327.38333333333333</v>
+        <v>297.23333333333335</v>
       </c>
       <c r="C90">
-        <v>5.4563888888888892</v>
+        <v>4.9538888888888888</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>21265</v>
+        <v>16340</v>
       </c>
       <c r="B91">
-        <v>354.41666666666669</v>
+        <v>272.33333333333331</v>
       </c>
       <c r="C91">
-        <v>5.9069444444444441</v>
+        <v>4.5388888888888888</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>21377</v>
+        <v>17189</v>
       </c>
       <c r="B92">
-        <v>356.28333333333336</v>
+        <v>286.48333333333335</v>
       </c>
       <c r="C92">
-        <v>5.9380555555555556</v>
+        <v>4.7747222222222225</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>22322</v>
+        <v>15984</v>
       </c>
       <c r="B93">
-        <v>372.03333333333336</v>
+        <v>266.39999999999998</v>
       </c>
       <c r="C93">
-        <v>6.2005555555555558</v>
+        <v>4.4400000000000004</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>16545</v>
+        <v>17181</v>
       </c>
       <c r="B94">
-        <v>275.75</v>
+        <v>286.35000000000002</v>
       </c>
       <c r="C94">
-        <v>4.5958333333333332</v>
+        <v>4.7725</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>19903</v>
+        <v>17910</v>
       </c>
       <c r="B95">
-        <v>331.71666666666664</v>
+        <v>298.5</v>
       </c>
       <c r="C95">
-        <v>5.5286111111111111</v>
+        <v>4.9749999999999996</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>21530</v>
+        <v>18310</v>
       </c>
       <c r="B96">
-        <v>358.83333333333331</v>
+        <v>305.16666666666669</v>
       </c>
       <c r="C96">
-        <v>5.9805555555555552</v>
+        <v>5.0861111111111112</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>21976</v>
+        <v>15632</v>
       </c>
       <c r="B97">
-        <v>366.26666666666665</v>
+        <v>260.53333333333336</v>
       </c>
       <c r="C97">
-        <v>6.1044444444444448</v>
+        <v>4.3422222222222224</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>23243</v>
+        <v>17093</v>
       </c>
       <c r="B98">
-        <v>387.38333333333333</v>
+        <v>284.88333333333333</v>
       </c>
       <c r="C98">
-        <v>6.4563888888888892</v>
+        <v>4.7480555555555553</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>21561</v>
+        <v>23264</v>
       </c>
       <c r="B99">
-        <v>359.35</v>
+        <v>387.73333333333335</v>
       </c>
       <c r="C99">
-        <v>5.9891666666666667</v>
+        <v>6.4622222222222225</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>21740</v>
+        <v>15585</v>
       </c>
       <c r="B100">
-        <v>362.33333333333331</v>
+        <v>259.75</v>
       </c>
       <c r="C100">
-        <v>6.0388888888888888</v>
+        <v>4.3291666666666666</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>18463</v>
+        <v>12418</v>
       </c>
       <c r="B101">
-        <v>307.71666666666664</v>
+        <v>206.96666666666667</v>
       </c>
       <c r="C101">
-        <v>5.1286111111111108</v>
+        <v>3.4494444444444445</v>
       </c>
     </row>
   </sheetData>
@@ -3557,1102 +3416,1102 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>25479</v>
+        <v>19759</v>
       </c>
       <c r="B2">
-        <v>424.65</v>
+        <v>329.31666666666666</v>
       </c>
       <c r="C2">
-        <v>7.0774999999999997</v>
+        <v>5.4886111111111111</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>23572</v>
+        <v>21205</v>
       </c>
       <c r="B3">
-        <v>392.86666666666667</v>
+        <v>353.41666666666669</v>
       </c>
       <c r="C3">
-        <v>6.5477777777777781</v>
+        <v>5.8902777777777775</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>22680</v>
+        <v>24775</v>
       </c>
       <c r="B4">
-        <v>378</v>
+        <v>412.91666666666669</v>
       </c>
       <c r="C4">
-        <v>6.3</v>
+        <v>6.8819444444444446</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>27111</v>
+        <v>20404</v>
       </c>
       <c r="B5">
-        <v>451.85</v>
+        <v>340.06666666666666</v>
       </c>
       <c r="C5">
-        <v>7.5308333333333337</v>
+        <v>5.6677777777777774</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>27574</v>
+        <v>19818</v>
       </c>
       <c r="B6">
-        <v>459.56666666666666</v>
+        <v>330.3</v>
       </c>
       <c r="C6">
-        <v>7.6594444444444445</v>
+        <v>5.5049999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>22561</v>
+        <v>19107</v>
       </c>
       <c r="B7">
-        <v>376.01666666666665</v>
+        <v>318.45</v>
       </c>
       <c r="C7">
-        <v>6.2669444444444444</v>
+        <v>5.3075000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>29898</v>
+        <v>15866</v>
       </c>
       <c r="B8">
-        <v>498.3</v>
+        <v>264.43333333333334</v>
       </c>
       <c r="C8">
-        <v>8.3049999999999997</v>
+        <v>4.4072222222222219</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>22356</v>
+        <v>20245</v>
       </c>
       <c r="B9">
-        <v>372.6</v>
+        <v>337.41666666666669</v>
       </c>
       <c r="C9">
-        <v>6.21</v>
+        <v>5.6236111111111109</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>29340</v>
+        <v>19851</v>
       </c>
       <c r="B10">
-        <v>489</v>
+        <v>330.85</v>
       </c>
       <c r="C10">
-        <v>8.15</v>
+        <v>5.5141666666666671</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>23133</v>
+        <v>18618</v>
       </c>
       <c r="B11">
-        <v>385.55</v>
+        <v>310.3</v>
       </c>
       <c r="C11">
-        <v>6.4258333333333333</v>
+        <v>5.1716666666666669</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>30543</v>
+        <v>18521</v>
       </c>
       <c r="B12">
-        <v>509.05</v>
+        <v>308.68333333333334</v>
       </c>
       <c r="C12">
-        <v>8.4841666666666669</v>
+        <v>5.1447222222222226</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>29016</v>
+        <v>20627</v>
       </c>
       <c r="B13">
-        <v>483.6</v>
+        <v>343.78333333333336</v>
       </c>
       <c r="C13">
-        <v>8.06</v>
+        <v>5.7297222222222226</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>22487</v>
+        <v>18372</v>
       </c>
       <c r="B14">
-        <v>374.78333333333336</v>
+        <v>306.2</v>
       </c>
       <c r="C14">
-        <v>6.2463888888888892</v>
+        <v>5.1033333333333335</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>22189</v>
+        <v>18594</v>
       </c>
       <c r="B15">
-        <v>369.81666666666666</v>
+        <v>309.89999999999998</v>
       </c>
       <c r="C15">
-        <v>6.1636111111111109</v>
+        <v>5.165</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>21234</v>
+        <v>21549</v>
       </c>
       <c r="B16">
-        <v>353.9</v>
+        <v>359.15</v>
       </c>
       <c r="C16">
-        <v>5.8983333333333334</v>
+        <v>5.9858333333333329</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>24318</v>
+        <v>19314</v>
       </c>
       <c r="B17">
-        <v>405.3</v>
+        <v>321.89999999999998</v>
       </c>
       <c r="C17">
-        <v>6.7549999999999999</v>
+        <v>5.3650000000000002</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>22289</v>
+        <v>19146</v>
       </c>
       <c r="B18">
-        <v>371.48333333333335</v>
+        <v>319.10000000000002</v>
       </c>
       <c r="C18">
-        <v>6.1913888888888886</v>
+        <v>5.3183333333333334</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>25336</v>
+        <v>20854</v>
       </c>
       <c r="B19">
-        <v>422.26666666666665</v>
+        <v>347.56666666666666</v>
       </c>
       <c r="C19">
-        <v>7.0377777777777775</v>
+        <v>5.7927777777777774</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>25372</v>
+        <v>22689</v>
       </c>
       <c r="B20">
-        <v>422.86666666666667</v>
+        <v>378.15</v>
       </c>
       <c r="C20">
-        <v>7.0477777777777781</v>
+        <v>6.3025000000000002</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>19683</v>
+        <v>21217</v>
       </c>
       <c r="B21">
-        <v>328.05</v>
+        <v>353.61666666666667</v>
       </c>
       <c r="C21">
-        <v>5.4675000000000002</v>
+        <v>5.8936111111111114</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>25776</v>
+        <v>18080</v>
       </c>
       <c r="B22">
-        <v>429.6</v>
+        <v>301.33333333333331</v>
       </c>
       <c r="C22">
-        <v>7.16</v>
+        <v>5.0222222222222221</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>26909</v>
+        <v>19725</v>
       </c>
       <c r="B23">
-        <v>448.48333333333335</v>
+        <v>328.75</v>
       </c>
       <c r="C23">
-        <v>7.4747222222222218</v>
+        <v>5.479166666666667</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>28253</v>
+        <v>19012</v>
       </c>
       <c r="B24">
-        <v>470.88333333333333</v>
+        <v>316.86666666666667</v>
       </c>
       <c r="C24">
-        <v>7.8480555555555558</v>
+        <v>5.2811111111111115</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>27650</v>
+        <v>27235</v>
       </c>
       <c r="B25">
-        <v>460.83333333333331</v>
+        <v>453.91666666666669</v>
       </c>
       <c r="C25">
-        <v>7.6805555555555554</v>
+        <v>7.5652777777777782</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>26881</v>
+        <v>19424</v>
       </c>
       <c r="B26">
-        <v>448.01666666666665</v>
+        <v>323.73333333333335</v>
       </c>
       <c r="C26">
-        <v>7.4669444444444446</v>
+        <v>5.3955555555555552</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>10800</v>
+        <v>21139</v>
       </c>
       <c r="B27">
-        <v>180</v>
+        <v>352.31666666666666</v>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>5.8719444444444449</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>24028</v>
+        <v>9685</v>
       </c>
       <c r="B28">
-        <v>400.46666666666664</v>
+        <v>161.41666666666666</v>
       </c>
       <c r="C28">
-        <v>6.6744444444444442</v>
+        <v>2.6902777777777778</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>32241</v>
+        <v>19560</v>
       </c>
       <c r="B29">
-        <v>537.35</v>
+        <v>326</v>
       </c>
       <c r="C29">
-        <v>8.9558333333333326</v>
+        <v>5.4333333333333336</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>27336</v>
+        <v>20743</v>
       </c>
       <c r="B30">
-        <v>455.6</v>
+        <v>345.71666666666664</v>
       </c>
       <c r="C30">
-        <v>7.5933333333333337</v>
+        <v>5.7619444444444445</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>26020</v>
+        <v>20309</v>
       </c>
       <c r="B31">
-        <v>433.66666666666669</v>
+        <v>338.48333333333335</v>
       </c>
       <c r="C31">
-        <v>7.2277777777777779</v>
+        <v>5.6413888888888888</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>27785</v>
+        <v>19334</v>
       </c>
       <c r="B32">
-        <v>463.08333333333331</v>
+        <v>322.23333333333335</v>
       </c>
       <c r="C32">
-        <v>7.7180555555555559</v>
+        <v>5.3705555555555557</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>36116</v>
+        <v>19855</v>
       </c>
       <c r="B33">
-        <v>601.93333333333328</v>
+        <v>330.91666666666669</v>
       </c>
       <c r="C33">
-        <v>10.032222222222222</v>
+        <v>5.5152777777777775</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>23131</v>
+        <v>21295</v>
       </c>
       <c r="B34">
-        <v>385.51666666666665</v>
+        <v>354.91666666666669</v>
       </c>
       <c r="C34">
-        <v>6.4252777777777776</v>
+        <v>5.9152777777777779</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>23689</v>
+        <v>19548</v>
       </c>
       <c r="B35">
-        <v>394.81666666666666</v>
+        <v>325.8</v>
       </c>
       <c r="C35">
-        <v>6.5802777777777779</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>25583</v>
+        <v>20794</v>
       </c>
       <c r="B36">
-        <v>426.38333333333333</v>
+        <v>346.56666666666666</v>
       </c>
       <c r="C36">
-        <v>7.1063888888888886</v>
+        <v>5.7761111111111108</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>26749</v>
+        <v>17858</v>
       </c>
       <c r="B37">
-        <v>445.81666666666666</v>
+        <v>297.63333333333333</v>
       </c>
       <c r="C37">
-        <v>7.4302777777777775</v>
+        <v>4.9605555555555556</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>21655</v>
+        <v>20599</v>
       </c>
       <c r="B38">
-        <v>360.91666666666669</v>
+        <v>343.31666666666666</v>
       </c>
       <c r="C38">
-        <v>6.0152777777777775</v>
+        <v>5.7219444444444445</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>6792</v>
+        <v>20101</v>
       </c>
       <c r="B39">
-        <v>113.2</v>
+        <v>335.01666666666665</v>
       </c>
       <c r="C39">
-        <v>1.8866666666666667</v>
+        <v>5.5836111111111109</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>26589</v>
+        <v>19031</v>
       </c>
       <c r="B40">
-        <v>443.15</v>
+        <v>317.18333333333334</v>
       </c>
       <c r="C40">
-        <v>7.3858333333333333</v>
+        <v>5.2863888888888892</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>24613</v>
+        <v>20483</v>
       </c>
       <c r="B41">
-        <v>410.21666666666664</v>
+        <v>341.38333333333333</v>
       </c>
       <c r="C41">
-        <v>6.8369444444444447</v>
+        <v>5.6897222222222226</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>24126</v>
+        <v>20248</v>
       </c>
       <c r="B42">
-        <v>402.1</v>
+        <v>337.46666666666664</v>
       </c>
       <c r="C42">
-        <v>6.7016666666666671</v>
+        <v>5.6244444444444444</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>22769</v>
+        <v>18191</v>
       </c>
       <c r="B43">
-        <v>379.48333333333335</v>
+        <v>303.18333333333334</v>
       </c>
       <c r="C43">
-        <v>6.3247222222222224</v>
+        <v>5.0530555555555559</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>34003</v>
+        <v>21878</v>
       </c>
       <c r="B44">
-        <v>566.7166666666667</v>
+        <v>364.63333333333333</v>
       </c>
       <c r="C44">
-        <v>9.4452777777777772</v>
+        <v>6.0772222222222219</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>23840</v>
+        <v>25490</v>
       </c>
       <c r="B45">
-        <v>397.33333333333331</v>
+        <v>424.83333333333331</v>
       </c>
       <c r="C45">
-        <v>6.6222222222222218</v>
+        <v>7.0805555555555557</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>24015</v>
+        <v>6782</v>
       </c>
       <c r="B46">
-        <v>400.25</v>
+        <v>113.03333333333333</v>
       </c>
       <c r="C46">
-        <v>6.6708333333333334</v>
+        <v>1.8838888888888889</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>27152</v>
+        <v>20208</v>
       </c>
       <c r="B47">
-        <v>452.53333333333336</v>
+        <v>336.8</v>
       </c>
       <c r="C47">
-        <v>7.5422222222222226</v>
+        <v>5.6133333333333333</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>24951</v>
+        <v>18593</v>
       </c>
       <c r="B48">
-        <v>415.85</v>
+        <v>309.88333333333333</v>
       </c>
       <c r="C48">
-        <v>6.9308333333333332</v>
+        <v>5.1647222222222222</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>22722</v>
+        <v>20634</v>
       </c>
       <c r="B49">
-        <v>378.7</v>
+        <v>343.9</v>
       </c>
       <c r="C49">
-        <v>6.3116666666666665</v>
+        <v>5.7316666666666665</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>25137</v>
+        <v>18676</v>
       </c>
       <c r="B50">
-        <v>418.95</v>
+        <v>311.26666666666665</v>
       </c>
       <c r="C50">
-        <v>6.9824999999999999</v>
+        <v>5.1877777777777778</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>23155</v>
+        <v>24730</v>
       </c>
       <c r="B51">
-        <v>385.91666666666669</v>
+        <v>412.16666666666669</v>
       </c>
       <c r="C51">
-        <v>6.4319444444444445</v>
+        <v>6.8694444444444445</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>23006</v>
+        <v>18222</v>
       </c>
       <c r="B52">
-        <v>383.43333333333334</v>
+        <v>303.7</v>
       </c>
       <c r="C52">
-        <v>6.3905555555555553</v>
+        <v>5.0616666666666665</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>27796</v>
+        <v>17495</v>
       </c>
       <c r="B53">
-        <v>463.26666666666665</v>
+        <v>291.58333333333331</v>
       </c>
       <c r="C53">
-        <v>7.721111111111111</v>
+        <v>4.8597222222222225</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>29204</v>
+        <v>24203</v>
       </c>
       <c r="B54">
-        <v>486.73333333333335</v>
+        <v>403.38333333333333</v>
       </c>
       <c r="C54">
-        <v>8.112222222222222</v>
+        <v>6.7230555555555558</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>28927</v>
+        <v>22361</v>
       </c>
       <c r="B55">
-        <v>482.11666666666667</v>
+        <v>372.68333333333334</v>
       </c>
       <c r="C55">
-        <v>8.0352777777777771</v>
+        <v>6.2113888888888891</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>22924</v>
+        <v>18318</v>
       </c>
       <c r="B56">
-        <v>382.06666666666666</v>
+        <v>305.3</v>
       </c>
       <c r="C56">
-        <v>6.3677777777777775</v>
+        <v>5.0883333333333329</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>33235</v>
+        <v>18741</v>
       </c>
       <c r="B57">
-        <v>553.91666666666663</v>
+        <v>312.35000000000002</v>
       </c>
       <c r="C57">
-        <v>9.2319444444444443</v>
+        <v>5.2058333333333335</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>22867</v>
+        <v>22015</v>
       </c>
       <c r="B58">
-        <v>381.11666666666667</v>
+        <v>366.91666666666669</v>
       </c>
       <c r="C58">
-        <v>6.3519444444444444</v>
+        <v>6.115277777777778</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>20071</v>
+        <v>20920</v>
       </c>
       <c r="B59">
-        <v>334.51666666666665</v>
+        <v>348.66666666666669</v>
       </c>
       <c r="C59">
-        <v>5.575277777777778</v>
+        <v>5.8111111111111109</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>21999</v>
+        <v>19273</v>
       </c>
       <c r="B60">
-        <v>366.65</v>
+        <v>321.21666666666664</v>
       </c>
       <c r="C60">
-        <v>6.1108333333333329</v>
+        <v>5.3536111111111113</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>34240</v>
+        <v>19909</v>
       </c>
       <c r="B61">
-        <v>570.66666666666663</v>
+        <v>331.81666666666666</v>
       </c>
       <c r="C61">
-        <v>9.5111111111111111</v>
+        <v>5.5302777777777781</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>29276</v>
+        <v>21759</v>
       </c>
       <c r="B62">
-        <v>487.93333333333334</v>
+        <v>362.65</v>
       </c>
       <c r="C62">
-        <v>8.1322222222222216</v>
+        <v>6.0441666666666665</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>31260</v>
+        <v>17351</v>
       </c>
       <c r="B63">
-        <v>521</v>
+        <v>289.18333333333334</v>
       </c>
       <c r="C63">
-        <v>8.6833333333333336</v>
+        <v>4.8197222222222225</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>27076</v>
+        <v>22677</v>
       </c>
       <c r="B64">
-        <v>451.26666666666665</v>
+        <v>377.95</v>
       </c>
       <c r="C64">
-        <v>7.5211111111111109</v>
+        <v>6.2991666666666664</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>18543</v>
+        <v>22067</v>
       </c>
       <c r="B65">
-        <v>309.05</v>
+        <v>367.78333333333336</v>
       </c>
       <c r="C65">
-        <v>5.1508333333333329</v>
+        <v>6.1297222222222221</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>28416</v>
+        <v>18337</v>
       </c>
       <c r="B66">
-        <v>473.6</v>
+        <v>305.61666666666667</v>
       </c>
       <c r="C66">
-        <v>7.8933333333333335</v>
+        <v>5.0936111111111115</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>25600</v>
+        <v>18601</v>
       </c>
       <c r="B67">
-        <v>426.66666666666669</v>
+        <v>310.01666666666665</v>
       </c>
       <c r="C67">
-        <v>7.1111111111111107</v>
+        <v>5.1669444444444448</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>32846</v>
+        <v>18654</v>
       </c>
       <c r="B68">
-        <v>547.43333333333328</v>
+        <v>310.89999999999998</v>
       </c>
       <c r="C68">
-        <v>9.1238888888888887</v>
+        <v>5.1816666666666666</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>22337</v>
+        <v>20312</v>
       </c>
       <c r="B69">
-        <v>372.28333333333336</v>
+        <v>338.53333333333336</v>
       </c>
       <c r="C69">
-        <v>6.2047222222222222</v>
+        <v>5.6422222222222222</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>23836</v>
+        <v>19596</v>
       </c>
       <c r="B70">
-        <v>397.26666666666665</v>
+        <v>326.60000000000002</v>
       </c>
       <c r="C70">
-        <v>6.6211111111111114</v>
+        <v>5.4433333333333334</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>24079</v>
+        <v>17557</v>
       </c>
       <c r="B71">
-        <v>401.31666666666666</v>
+        <v>292.61666666666667</v>
       </c>
       <c r="C71">
-        <v>6.6886111111111113</v>
+        <v>4.8769444444444447</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>20540</v>
+        <v>19684</v>
       </c>
       <c r="B72">
-        <v>342.33333333333331</v>
+        <v>328.06666666666666</v>
       </c>
       <c r="C72">
-        <v>5.7055555555555557</v>
+        <v>5.4677777777777781</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>26668</v>
+        <v>18818</v>
       </c>
       <c r="B73">
-        <v>444.46666666666664</v>
+        <v>313.63333333333333</v>
       </c>
       <c r="C73">
-        <v>7.4077777777777776</v>
+        <v>5.2272222222222222</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>22659</v>
+        <v>18888</v>
       </c>
       <c r="B74">
-        <v>377.65</v>
+        <v>314.8</v>
       </c>
       <c r="C74">
-        <v>6.2941666666666665</v>
+        <v>5.246666666666667</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>31241</v>
+        <v>20777</v>
       </c>
       <c r="B75">
-        <v>520.68333333333328</v>
+        <v>346.28333333333336</v>
       </c>
       <c r="C75">
-        <v>8.6780555555555559</v>
+        <v>5.7713888888888887</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>21113</v>
+        <v>19199</v>
       </c>
       <c r="B76">
-        <v>351.88333333333333</v>
+        <v>319.98333333333335</v>
       </c>
       <c r="C76">
-        <v>5.8647222222222224</v>
+        <v>5.3330555555555552</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>25566</v>
+        <v>20639</v>
       </c>
       <c r="B77">
-        <v>426.1</v>
+        <v>343.98333333333335</v>
       </c>
       <c r="C77">
-        <v>7.1016666666666666</v>
+        <v>5.7330555555555556</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>23726</v>
+        <v>19413</v>
       </c>
       <c r="B78">
-        <v>395.43333333333334</v>
+        <v>323.55</v>
       </c>
       <c r="C78">
-        <v>6.5905555555555555</v>
+        <v>5.3925000000000001</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>36392</v>
+        <v>24694</v>
       </c>
       <c r="B79">
-        <v>606.5333333333333</v>
+        <v>411.56666666666666</v>
       </c>
       <c r="C79">
-        <v>10.108888888888888</v>
+        <v>6.8594444444444447</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>16003</v>
+        <v>18393</v>
       </c>
       <c r="B80">
-        <v>266.71666666666664</v>
+        <v>306.55</v>
       </c>
       <c r="C80">
-        <v>4.4452777777777781</v>
+        <v>5.1091666666666669</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>34629</v>
+        <v>20395</v>
       </c>
       <c r="B81">
-        <v>577.15</v>
+        <v>339.91666666666669</v>
       </c>
       <c r="C81">
-        <v>9.6191666666666666</v>
+        <v>5.6652777777777779</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>25312</v>
+        <v>22067</v>
       </c>
       <c r="B82">
-        <v>421.86666666666667</v>
+        <v>367.78333333333336</v>
       </c>
       <c r="C82">
-        <v>7.0311111111111115</v>
+        <v>6.1297222222222221</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>28024</v>
+        <v>20997</v>
       </c>
       <c r="B83">
-        <v>467.06666666666666</v>
+        <v>349.95</v>
       </c>
       <c r="C83">
-        <v>7.7844444444444445</v>
+        <v>5.8324999999999996</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>29907</v>
+        <v>23621</v>
       </c>
       <c r="B84">
-        <v>498.45</v>
+        <v>393.68333333333334</v>
       </c>
       <c r="C84">
-        <v>8.3074999999999992</v>
+        <v>6.5613888888888887</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>26474</v>
+        <v>19785</v>
       </c>
       <c r="B85">
-        <v>441.23333333333335</v>
+        <v>329.75</v>
       </c>
       <c r="C85">
-        <v>7.3538888888888891</v>
+        <v>5.4958333333333336</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>28268</v>
+        <v>19621</v>
       </c>
       <c r="B86">
-        <v>471.13333333333333</v>
+        <v>327.01666666666665</v>
       </c>
       <c r="C86">
-        <v>7.8522222222222222</v>
+        <v>5.450277777777778</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>25454</v>
+        <v>21327</v>
       </c>
       <c r="B87">
-        <v>424.23333333333335</v>
+        <v>355.45</v>
       </c>
       <c r="C87">
-        <v>7.0705555555555559</v>
+        <v>5.9241666666666664</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>24429</v>
+        <v>21650</v>
       </c>
       <c r="B88">
-        <v>407.15</v>
+        <v>360.83333333333331</v>
       </c>
       <c r="C88">
-        <v>6.7858333333333336</v>
+        <v>6.0138888888888893</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>6744</v>
+        <v>22856</v>
       </c>
       <c r="B89">
-        <v>112.4</v>
+        <v>380.93333333333334</v>
       </c>
       <c r="C89">
-        <v>1.8733333333333333</v>
+        <v>6.3488888888888892</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>29995</v>
+        <v>18524</v>
       </c>
       <c r="B90">
-        <v>499.91666666666669</v>
+        <v>308.73333333333335</v>
       </c>
       <c r="C90">
-        <v>8.3319444444444439</v>
+        <v>5.1455555555555552</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>28028</v>
+        <v>20209</v>
       </c>
       <c r="B91">
-        <v>467.13333333333333</v>
+        <v>336.81666666666666</v>
       </c>
       <c r="C91">
-        <v>7.7855555555555558</v>
+        <v>5.6136111111111111</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>7447</v>
+        <v>22606</v>
       </c>
       <c r="B92">
-        <v>124.11666666666666</v>
+        <v>376.76666666666665</v>
       </c>
       <c r="C92">
-        <v>2.0686111111111112</v>
+        <v>6.2794444444444446</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>30418</v>
+        <v>21839</v>
       </c>
       <c r="B93">
-        <v>506.96666666666664</v>
+        <v>363.98333333333335</v>
       </c>
       <c r="C93">
-        <v>8.4494444444444436</v>
+        <v>6.0663888888888886</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>31855</v>
+        <v>23308</v>
       </c>
       <c r="B94">
-        <v>530.91666666666663</v>
+        <v>388.46666666666664</v>
       </c>
       <c r="C94">
-        <v>8.8486111111111114</v>
+        <v>6.474444444444444</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>22513</v>
+        <v>17418</v>
       </c>
       <c r="B95">
-        <v>375.21666666666664</v>
+        <v>290.3</v>
       </c>
       <c r="C95">
-        <v>6.2536111111111108</v>
+        <v>4.8383333333333329</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>36457</v>
+        <v>20593</v>
       </c>
       <c r="B96">
-        <v>607.61666666666667</v>
+        <v>343.21666666666664</v>
       </c>
       <c r="C96">
-        <v>10.126944444444444</v>
+        <v>5.7202777777777776</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>30821</v>
+        <v>19385</v>
       </c>
       <c r="B97">
-        <v>513.68333333333328</v>
+        <v>323.08333333333331</v>
       </c>
       <c r="C97">
-        <v>8.5613888888888887</v>
+        <v>5.384722222222222</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>31131</v>
+        <v>20579</v>
       </c>
       <c r="B98">
-        <v>518.85</v>
+        <v>342.98333333333335</v>
       </c>
       <c r="C98">
-        <v>8.6475000000000009</v>
+        <v>5.716388888888889</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>27318</v>
+        <v>18450</v>
       </c>
       <c r="B99">
-        <v>455.3</v>
+        <v>307.5</v>
       </c>
       <c r="C99">
-        <v>7.5883333333333329</v>
+        <v>5.125</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>28223</v>
+        <v>19071</v>
       </c>
       <c r="B100">
-        <v>470.38333333333333</v>
+        <v>317.85000000000002</v>
       </c>
       <c r="C100">
-        <v>7.839722222222222</v>
+        <v>5.2975000000000003</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>17486</v>
+        <v>19449</v>
       </c>
       <c r="B101">
-        <v>291.43333333333334</v>
+        <v>324.14999999999998</v>
       </c>
       <c r="C101">
-        <v>4.8572222222222221</v>
+        <v>5.4024999999999999</v>
       </c>
     </row>
   </sheetData>
